--- a/results/tables/table3_main_results.xlsx
+++ b/results/tables/table3_main_results.xlsx
@@ -100,7 +100,7 @@
     <t>streak_ge60</t>
   </si>
   <si>
-    <t>crisis_media_lag0 (within-emergency, H4)</t>
+    <t>devrel_media_contemp x emergency (H4 difference, stacked PPML)</t>
   </si>
   <si>
     <t>extensive margin</t>
@@ -163,7 +163,7 @@
     <t>0.202* (0.100)</t>
   </si>
   <si>
-    <t>0.097** (0.037)</t>
+    <t>0.674*** (0.141)</t>
   </si>
   <si>
     <t>0.008 (0.010)</t>
@@ -859,19 +859,19 @@
         <v>28</v>
       </c>
       <c r="C13">
-        <v>0.0966519096493873</v>
+        <v>0.6738258640553701</v>
       </c>
       <c r="D13">
-        <v>0.0368865974240931</v>
+        <v>0.1406223479559541</v>
       </c>
       <c r="E13">
-        <v>0.008855971894480201</v>
+        <v>1.653402928791792E-06</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G13">
-        <v>2080</v>
+        <v>4122</v>
       </c>
       <c r="H13" t="s">
         <v>49</v>
